--- a/anthropic/2026-10-11/Anthropic_IPO_Basic_Valuation.xlsx
+++ b/anthropic/2026-10-11/Anthropic_IPO_Basic_Valuation.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="1" r:id="R587c4db865c54ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="2" r:id="R4435dffdbcd4489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" r:id="R1abdb312155d4fa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="1" r:id="Rcd6d0f44ea1e40f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="2" r:id="R46aee4bb4e8d4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" r:id="R7984c7315c3a422b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="10">
+  <x:numFmts count="13">
     <x:numFmt numFmtId="200" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <x:numFmt numFmtId="201" formatCode="dd-mmm-yyyy"/>
     <x:numFmt numFmtId="202" formatCode="$#,##0.0;($#,##0.0);&quot;-&quot;"/>
@@ -26,6 +26,9 @@
     <x:numFmt numFmtId="207" formatCode="$0.000"/>
     <x:numFmt numFmtId="208" formatCode="0&quot;E&quot;"/>
     <x:numFmt numFmtId="209" formatCode="$0.00;($0.00);&quot;-&quot;"/>
+    <x:numFmt numFmtId="210" formatCode="0.0"/>
+    <x:numFmt numFmtId="211" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="212" formatCode="0.0%"/>
   </x:numFmts>
   <x:fonts count="20">
     <x:font>
@@ -199,7 +202,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="123">
+  <x:cellXfs count="127">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -563,6 +566,18 @@
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -920,7 +935,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c48586677df4755"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc1d740eac1294e9c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -950,7 +965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R44b75ae41e664c8b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8762bb2124e5426d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1348,15 +1363,15 @@
       <x:c r="A10" s="3"/>
       <x:c r="B10" s="3"/>
       <x:c r="C10" s="3" t="str">
-        <x:v>Reported IPO equity benchmark</x:v>
+        <x:v>IPO investor discussion</x:v>
       </x:c>
       <x:c r="D10" s="55" t="n">
         <x:f>'Inputs'!D15</x:f>
-        <x:v>2000</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="26" t="str">
-        <x:v>Reference target. Final offer price is unavailable.</x:v>
+        <x:v>Investor discussion; no priced offering or company valuation guidance.</x:v>
       </x:c>
       <x:c r="G10" s="4"/>
       <x:c r="H10" s="4"/>
@@ -1375,7 +1390,7 @@
       </x:c>
       <x:c r="D11" s="73" t="n">
         <x:f>D25/D10-1</x:f>
-        <x:v>-0.025000000000000022</x:v>
+        <x:v>0.30000000000000004</x:v>
       </x:c>
       <x:c r="E11" s="4"/>
       <x:c r="F11" s="26" t="str">
@@ -1398,7 +1413,7 @@
       </x:c>
       <x:c r="D12" s="73" t="n">
         <x:f>IF(ISNUMBER(D58),D58/D10-1,"n.a.")</x:f>
-        <x:v>-0.6057302778002258</x:v>
+        <x:v>-0.47430703706696764</x:v>
       </x:c>
       <x:c r="E12" s="4"/>
       <x:c r="F12" s="26" t="str">
@@ -1421,11 +1436,11 @@
       </x:c>
       <x:c r="D13" s="73" t="n">
         <x:f>D9/D10-1</x:f>
-        <x:v>-0.05714285714285727</x:v>
+        <x:v>0.2571428571428571</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="26" t="str">
-        <x:v>Comps sits below the benchmark; DCF sits far below both.</x:v>
+        <x:v>Heterogeneous peer references; excluded from Zhipu transaction multiples.</x:v>
       </x:c>
       <x:c r="G13" s="4"/>
       <x:c r="H13" s="4"/>
@@ -1444,7 +1459,7 @@
       </x:c>
       <x:c r="D14" s="74" t="n">
         <x:f>(D10-D24)/D21</x:f>
-        <x:v>10.256410256410257</x:v>
+        <x:v>7.6923076923076925</x:v>
       </x:c>
       <x:c r="E14" s="4"/>
       <x:c r="F14" s="26" t="str">
@@ -2393,7 +2408,7 @@
       </x:c>
       <x:c r="K42" s="94" t="n">
         <x:f>(1+'Inputs'!$D$11)^(-K41)</x:f>
-        <x:v>0.4523492153368933</x:v>
+        <x:v>0.4523492153368934</x:v>
       </x:c>
       <x:c r="L42" s="94" t="n">
         <x:f>(1+'Inputs'!$D$11)^(-L41)</x:f>
@@ -2441,7 +2456,7 @@
       </x:c>
       <x:c r="K43" s="70" t="n">
         <x:f>K40*K42</x:f>
-        <x:v>45.91016441129217</x:v>
+        <x:v>45.91016441129218</x:v>
       </x:c>
       <x:c r="L43" s="70" t="n">
         <x:f>L40*L42</x:f>
@@ -2796,7 +2811,7 @@
       </x:c>
       <x:c r="D60" s="61" t="n">
         <x:f>IF('Inputs'!D11&gt;'Inputs'!D13,(D10-D24-D56)/N42*('Inputs'!D11-'Inputs'!D13),"n.a.")</x:f>
-        <x:v>464.8075623130818</x:v>
+        <x:v>325.0443929375923</x:v>
       </x:c>
       <x:c r="E60" s="4"/>
       <x:c r="F60" s="26" t="str">
@@ -2819,7 +2834,7 @@
       </x:c>
       <x:c r="D61" s="91" t="n">
         <x:f>IF(ISNUMBER(D60),(D60-SUM(D50:D52))/D46/(1-'Inputs'!D14),"n.a.")</x:f>
-        <x:v>1.1083558835579803</x:v>
+        <x:v>0.7953634877048167</x:v>
       </x:c>
       <x:c r="E61" s="4"/>
       <x:c r="F61" s="26" t="str">
@@ -3498,7 +3513,7 @@
       </x:c>
       <x:c r="E91" s="97" t="n">
         <x:f>IF(ISNUMBER(D91),D91/$D$10-1,"n.a.")</x:f>
-        <x:v>-0.6057302778002258</x:v>
+        <x:v>-0.47430703706696764</x:v>
       </x:c>
       <x:c r="F91" s="4"/>
       <x:c r="G91" s="4"/>
@@ -3522,7 +3537,7 @@
       </x:c>
       <x:c r="E92" s="97" t="n">
         <x:f>IF(ISNUMBER(D92),D92/$D$10-1,"n.a.")</x:f>
-        <x:v>-0.6098383604021655</x:v>
+        <x:v>-0.4797844805362207</x:v>
       </x:c>
       <x:c r="F92" s="4"/>
       <x:c r="G92" s="4"/>
@@ -3546,7 +3561,7 @@
       </x:c>
       <x:c r="E93" s="97" t="n">
         <x:f>IF(ISNUMBER(D93),D93/$D$10-1,"n.a.")</x:f>
-        <x:v>-0.05714285714285727</x:v>
+        <x:v>0.2571428571428571</x:v>
       </x:c>
       <x:c r="F93" s="4"/>
       <x:c r="G93" s="4"/>
@@ -3570,7 +3585,7 @@
       </x:c>
       <x:c r="E94" s="97" t="n">
         <x:f>IF(ISNUMBER(D94),D94/$D$10-1,"n.a.")</x:f>
-        <x:v>0.33119999999999994</x:v>
+        <x:v>0.7749333333333335</x:v>
       </x:c>
       <x:c r="F94" s="4"/>
       <x:c r="G94" s="4"/>
@@ -3594,7 +3609,7 @@
       </x:c>
       <x:c r="E95" s="121" t="n">
         <x:f>IF(ISNUMBER(D95),D95/$D$10-1,"n.a.")</x:f>
-        <x:v>-0.05714285714285727</x:v>
+        <x:v>0.2571428571428571</x:v>
       </x:c>
       <x:c r="F95" s="4"/>
       <x:c r="G95" s="4"/>
@@ -3618,7 +3633,7 @@
       </x:c>
       <x:c r="E96" s="97" t="n">
         <x:f>IF(ISNUMBER(D96),D96/$D$10-1,"n.a.")</x:f>
-        <x:v>-0.5175000000000001</x:v>
+        <x:v>-0.3566666666666667</x:v>
       </x:c>
       <x:c r="F96" s="4"/>
       <x:c r="G96" s="4"/>
@@ -3642,7 +3657,7 @@
       </x:c>
       <x:c r="E97" s="97" t="n">
         <x:f>IF(ISNUMBER(D97),D97/$D$10-1,"n.a.")</x:f>
-        <x:v>-0.44999999999999996</x:v>
+        <x:v>-0.2666666666666667</x:v>
       </x:c>
       <x:c r="F97" s="4"/>
       <x:c r="G97" s="4"/>
@@ -3666,7 +3681,7 @@
       </x:c>
       <x:c r="E98" s="97" t="n">
         <x:f>IF(ISNUMBER(D98),D98/$D$10-1,"n.a.")</x:f>
-        <x:v>-0.09999999999999998</x:v>
+        <x:v>0.19999999999999996</x:v>
       </x:c>
       <x:c r="F98" s="4"/>
       <x:c r="G98" s="4"/>
@@ -3682,11 +3697,11 @@
       <x:c r="A99" s="3"/>
       <x:c r="B99" s="3"/>
       <x:c r="C99" s="3" t="str">
-        <x:v>IPO equity benchmark</x:v>
+        <x:v>IPO investor discussion</x:v>
       </x:c>
       <x:c r="D99" s="19" t="n">
         <x:f>D10</x:f>
-        <x:v>2000</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="E99" s="97" t="n">
         <x:f>IF(ISNUMBER(D99),D99/$D$10-1,"n.a.")</x:f>
@@ -3758,7 +3773,7 @@
       <x:c r="A103" s="3"/>
       <x:c r="B103" s="3"/>
       <x:c r="C103" s="9" t="str">
-        <x:v>The entire $2tn case rests on which peer tier the market assigns, not on the discount rate.</x:v>
+        <x:v>Latest investor discussion is USD1.5tn; the earlier USD2tn expectation is a historical stress case.</x:v>
       </x:c>
       <x:c r="D103" s="5"/>
       <x:c r="E103" s="5"/>
@@ -3841,7 +3856,9 @@
     <x:row r="108" ht="21" customHeight="1">
       <x:c r="A108" s="3"/>
       <x:c r="B108" s="3"/>
-      <x:c r="C108" s="3"/>
+      <x:c r="C108" s="3" t="str">
+        <x:v>Reported quarters and annual revenue assumption</x:v>
+      </x:c>
       <x:c r="D108" s="5"/>
       <x:c r="E108" s="5"/>
       <x:c r="F108" s="5"/>
@@ -3857,8 +3874,13 @@
     <x:row r="109" ht="21" customHeight="1">
       <x:c r="A109" s="3"/>
       <x:c r="B109" s="3"/>
-      <x:c r="C109" s="3"/>
-      <x:c r="D109" s="5"/>
+      <x:c r="C109" s="3" t="str">
+        <x:v>Reported Q1-Q3 revenue (USD bn)</x:v>
+      </x:c>
+      <x:c r="D109" s="125" t="n">
+        <x:f>SUM('Inputs'!J37:J39)</x:f>
+        <x:v>33.1</x:v>
+      </x:c>
       <x:c r="E109" s="5"/>
       <x:c r="F109" s="5"/>
       <x:c r="G109" s="5"/>
@@ -3873,8 +3895,13 @@
     <x:row r="110" ht="21" customHeight="1">
       <x:c r="A110" s="3"/>
       <x:c r="B110" s="3"/>
-      <x:c r="C110" s="3"/>
-      <x:c r="D110" s="5"/>
+      <x:c r="C110" s="3" t="str">
+        <x:v>FY2026 revenue assumption (USD bn)</x:v>
+      </x:c>
+      <x:c r="D110" s="125" t="n">
+        <x:f>'Inputs'!D22</x:f>
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="E110" s="5"/>
       <x:c r="F110" s="5"/>
       <x:c r="G110" s="5"/>
@@ -3889,8 +3916,13 @@
     <x:row r="111" ht="21" customHeight="1">
       <x:c r="A111" s="3"/>
       <x:c r="B111" s="3"/>
-      <x:c r="C111" s="3"/>
-      <x:c r="D111" s="5"/>
+      <x:c r="C111" s="3" t="str">
+        <x:v>Q4 revenue needed (USD bn)</x:v>
+      </x:c>
+      <x:c r="D111" s="125" t="n">
+        <x:f>D110-D109</x:f>
+        <x:v>30.9</x:v>
+      </x:c>
       <x:c r="E111" s="5"/>
       <x:c r="F111" s="5"/>
       <x:c r="G111" s="5"/>
@@ -3905,8 +3937,13 @@
     <x:row r="112" ht="21" customHeight="1">
       <x:c r="A112" s="3"/>
       <x:c r="B112" s="3"/>
-      <x:c r="C112" s="3"/>
-      <x:c r="D112" s="5"/>
+      <x:c r="C112" s="3" t="str">
+        <x:v>Required Q4 growth vs Q3</x:v>
+      </x:c>
+      <x:c r="D112" s="126" t="n">
+        <x:f>D111/'Inputs'!J39-1</x:f>
+        <x:v>0.8392857142857142</x:v>
+      </x:c>
       <x:c r="E112" s="5"/>
       <x:c r="F112" s="5"/>
       <x:c r="G112" s="5"/>
@@ -4220,7 +4257,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8efd57df475471d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40d1579a417e4415"/>
 </x:worksheet>
 </file>
 
@@ -7211,11 +7248,11 @@
         <x:v>Research cutoff</x:v>
       </x:c>
       <x:c r="D8" s="17" t="d">
-        <x:v>2026-10-11T00:00:00.000Z</x:v>
+        <x:v>2026-10-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="26" t="str">
-        <x:v>Public S-1 had not posted to EDGAR as of 9 Oct 2026 [S8]. No audited financials exist yet.</x:v>
+        <x:v>Reviewed through 16 Oct 2026 Beijing time; latest observations in S18/S19.</x:v>
       </x:c>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
@@ -7367,11 +7404,11 @@
       </x:c>
       <x:c r="D15" s="18" t="n">
         <x:f>D45</x:f>
-        <x:v>2000</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="E15" s="4"/>
       <x:c r="F15" s="26" t="str">
-        <x:v>$2tn reference from September reporting [S3]. Not a priced offer.</x:v>
+        <x:v>Investor discussion reported 16 Oct Beijing time [S18]; not a priced offer.</x:v>
       </x:c>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="4"/>
@@ -7751,7 +7788,7 @@
       <x:c r="A29" s="3"/>
       <x:c r="B29" s="3"/>
       <x:c r="C29" s="40" t="str">
-        <x:v>2026 revenue of $64bn is a model output, not a disclosure. It integrates the published run-rate path</x:v>
+        <x:v>2026 revenue of USD64bn remains an analyst assumption, not a reported annual result.</x:v>
       </x:c>
       <x:c r="D29" s="5"/>
       <x:c r="E29" s="5"/>
@@ -7769,7 +7806,7 @@
       <x:c r="A30" s="3"/>
       <x:c r="B30" s="3"/>
       <x:c r="C30" s="40" t="str">
-        <x:v>($9bn Dec-25, $20bn Mar-26, $30bn Apr-26, $47bn May-26, $65bn Jul-26, $100-120bn Dec-26E) over twelve months.</x:v>
+        <x:v>Latest quarterly observations and a full-year reconciliation appear below and on Valuation.</x:v>
       </x:c>
       <x:c r="D30" s="5"/>
       <x:c r="E30" s="5"/>
@@ -7890,11 +7927,21 @@
         <x:v>Source ID</x:v>
       </x:c>
       <x:c r="H36" s="5"/>
-      <x:c r="I36" s="5"/>
-      <x:c r="J36" s="5"/>
-      <x:c r="K36" s="5"/>
-      <x:c r="L36" s="5"/>
-      <x:c r="M36" s="5"/>
+      <x:c r="I36" s="32" t="str">
+        <x:v>Period</x:v>
+      </x:c>
+      <x:c r="J36" s="43" t="str">
+        <x:v>Revenue $bn</x:v>
+      </x:c>
+      <x:c r="K36" s="43" t="str">
+        <x:v>Available BJT</x:v>
+      </x:c>
+      <x:c r="L36" s="43" t="str">
+        <x:v>Classification</x:v>
+      </x:c>
+      <x:c r="M36" s="43" t="str">
+        <x:v>Source</x:v>
+      </x:c>
       <x:c r="N36" s="5"/>
     </x:row>
     <x:row r="37" ht="21" customHeight="1">
@@ -7916,11 +7963,21 @@
         <x:v>S3</x:v>
       </x:c>
       <x:c r="H37" s="5"/>
-      <x:c r="I37" s="5"/>
-      <x:c r="J37" s="5"/>
-      <x:c r="K37" s="5"/>
-      <x:c r="L37" s="5"/>
-      <x:c r="M37" s="5"/>
+      <x:c r="I37" s="3" t="str">
+        <x:v>2026Q1</x:v>
+      </x:c>
+      <x:c r="J37" s="123" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="K37" s="124" t="d">
+        <x:v>2026-10-15T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="L37" s="4" t="str">
+        <x:v>Media-reported</x:v>
+      </x:c>
+      <x:c r="M37" s="4" t="str">
+        <x:v>S19</x:v>
+      </x:c>
       <x:c r="N37" s="5"/>
     </x:row>
     <x:row r="38" ht="21" customHeight="1">
@@ -7942,11 +7999,21 @@
         <x:v>S3</x:v>
       </x:c>
       <x:c r="H38" s="5"/>
-      <x:c r="I38" s="5"/>
-      <x:c r="J38" s="5"/>
-      <x:c r="K38" s="5"/>
-      <x:c r="L38" s="5"/>
-      <x:c r="M38" s="5"/>
+      <x:c r="I38" s="3" t="str">
+        <x:v>2026Q2</x:v>
+      </x:c>
+      <x:c r="J38" s="123" t="n">
+        <x:v>11.6</x:v>
+      </x:c>
+      <x:c r="K38" s="124" t="d">
+        <x:v>2026-10-15T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="L38" s="4" t="str">
+        <x:v>Media-reported</x:v>
+      </x:c>
+      <x:c r="M38" s="4" t="str">
+        <x:v>S19</x:v>
+      </x:c>
       <x:c r="N38" s="5"/>
     </x:row>
     <x:row r="39" ht="21" customHeight="1">
@@ -7968,11 +8035,21 @@
         <x:v>S1</x:v>
       </x:c>
       <x:c r="H39" s="5"/>
-      <x:c r="I39" s="5"/>
-      <x:c r="J39" s="5"/>
-      <x:c r="K39" s="5"/>
-      <x:c r="L39" s="5"/>
-      <x:c r="M39" s="5"/>
+      <x:c r="I39" s="3" t="str">
+        <x:v>2026Q3</x:v>
+      </x:c>
+      <x:c r="J39" s="123" t="n">
+        <x:v>16.8</x:v>
+      </x:c>
+      <x:c r="K39" s="124" t="d">
+        <x:v>2026-10-15T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="L39" s="4" t="str">
+        <x:v>Media-reported</x:v>
+      </x:c>
+      <x:c r="M39" s="4" t="str">
+        <x:v>S19</x:v>
+      </x:c>
       <x:c r="N39" s="5"/>
     </x:row>
     <x:row r="40" ht="21" customHeight="1">
@@ -8109,19 +8186,19 @@
       <x:c r="A45" s="3"/>
       <x:c r="B45" s="3"/>
       <x:c r="C45" s="3" t="str">
-        <x:v>IPO equity benchmark, about</x:v>
+        <x:v>IPO investor discussion, about</x:v>
       </x:c>
       <x:c r="D45" s="44" t="n">
-        <x:v>2000</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="E45" s="45" t="str">
-        <x:v>Sep-26</x:v>
+        <x:v>16-Oct-26 BJT</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
-        <x:v>Reported target</x:v>
+        <x:v>Media-reported</x:v>
       </x:c>
       <x:c r="G45" s="4" t="str">
-        <x:v>S3</x:v>
+        <x:v>S18</x:v>
       </x:c>
       <x:c r="H45" s="5"/>
       <x:c r="I45" s="5"/>
@@ -8135,19 +8212,19 @@
       <x:c r="A46" s="3"/>
       <x:c r="B46" s="3"/>
       <x:c r="C46" s="3" t="str">
-        <x:v>Long-term compute commitments, over</x:v>
+        <x:v>Long-term compute commitments, at least</x:v>
       </x:c>
       <x:c r="D46" s="44" t="n">
-        <x:v>417</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E46" s="45" t="str">
-        <x:v>Early 2026</x:v>
+        <x:v>Oct-26</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
         <x:v>Media-reported</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
-        <x:v>S3</x:v>
+        <x:v>S19</x:v>
       </x:c>
       <x:c r="H46" s="5"/>
       <x:c r="I46" s="5"/>
@@ -9664,7 +9741,9 @@
     <x:row r="125" ht="21" customHeight="1">
       <x:c r="A125" s="3"/>
       <x:c r="B125" s="3"/>
-      <x:c r="C125" s="3"/>
+      <x:c r="C125" s="3" t="str">
+        <x:v>S18. Reuters, 15 Oct 21:00 UTC / 16 Oct 05:00 Beijing. IPO investor discussion.</x:v>
+      </x:c>
       <x:c r="D125" s="5"/>
       <x:c r="E125" s="5"/>
       <x:c r="F125" s="5"/>
@@ -9680,7 +9759,9 @@
     <x:row r="126" ht="21" customHeight="1">
       <x:c r="A126" s="3"/>
       <x:c r="B126" s="3"/>
-      <x:c r="C126" s="3"/>
+      <x:c r="C126" s="3" t="str">
+        <x:v>https://www.aol.com/articles/exclusive-investors-temper-anthropic-ipo-210007000.html</x:v>
+      </x:c>
       <x:c r="D126" s="5"/>
       <x:c r="E126" s="5"/>
       <x:c r="F126" s="5"/>
@@ -9712,7 +9793,9 @@
     <x:row r="128" ht="21" customHeight="1">
       <x:c r="A128" s="3"/>
       <x:c r="B128" s="3"/>
-      <x:c r="C128" s="3"/>
+      <x:c r="C128" s="3" t="str">
+        <x:v>S19. Reuters, 15 Oct Beijing. Quarterly revenue and decade-long compute commitments.</x:v>
+      </x:c>
       <x:c r="D128" s="5"/>
       <x:c r="E128" s="5"/>
       <x:c r="F128" s="5"/>
@@ -9728,7 +9811,9 @@
     <x:row r="129" ht="21" customHeight="1">
       <x:c r="A129" s="3"/>
       <x:c r="B129" s="3"/>
-      <x:c r="C129" s="3"/>
+      <x:c r="C129" s="3" t="str">
+        <x:v>https://uk.marketscreener.com/news/anthropic-s-q3-revenue-surges-45-to-nearly-17-billion-ce785dd2d08cf221</x:v>
+      </x:c>
       <x:c r="D129" s="5"/>
       <x:c r="E129" s="5"/>
       <x:c r="F129" s="5"/>

--- a/anthropic/2026-10-11/Anthropic_IPO_Basic_Valuation.xlsx
+++ b/anthropic/2026-10-11/Anthropic_IPO_Basic_Valuation.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="1" r:id="Rcd6d0f44ea1e40f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="2" r:id="R46aee4bb4e8d4d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" r:id="R7984c7315c3a422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="1" r:id="R156dd3a3bc414374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="2" r:id="Rab9a618d17d145b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" r:id="R9c8d8dfec6494bc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -935,7 +935,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc1d740eac1294e9c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc46b2f0bb52f41e5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -965,7 +965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8762bb2124e5426d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R03cba60d29ad459d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3974,7 +3974,9 @@
     <x:row r="114" ht="21" customHeight="1">
       <x:c r="A114" s="3"/>
       <x:c r="B114" s="3"/>
-      <x:c r="C114" s="3"/>
+      <x:c r="C114" s="3" t="str">
+        <x:v>23 Oct review: USD1.5tn discussion retained; new product/governance news does not change cash-flow inputs.</x:v>
+      </x:c>
       <x:c r="D114" s="5"/>
       <x:c r="E114" s="5"/>
       <x:c r="F114" s="5"/>
@@ -3990,7 +3992,9 @@
     <x:row r="115" ht="21" customHeight="1">
       <x:c r="A115" s="3"/>
       <x:c r="B115" s="3"/>
-      <x:c r="C115" s="3"/>
+      <x:c r="C115" s="3" t="str">
+        <x:v>Public-benefit share commitment is conditional; no mechanical 5% EV haircut or assumed dilution.</x:v>
+      </x:c>
       <x:c r="D115" s="5"/>
       <x:c r="E115" s="5"/>
       <x:c r="F115" s="5"/>
@@ -4006,7 +4010,9 @@
     <x:row r="116" ht="21" customHeight="1">
       <x:c r="A116" s="3"/>
       <x:c r="B116" s="3"/>
-      <x:c r="C116" s="3"/>
+      <x:c r="C116" s="3" t="str">
+        <x:v>The 26 Oct public S-1 is a subsequent event, excluded from the 23 Oct valuation information set.</x:v>
+      </x:c>
       <x:c r="D116" s="5"/>
       <x:c r="E116" s="5"/>
       <x:c r="F116" s="5"/>
@@ -4257,7 +4263,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40d1579a417e4415"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R499c812c8ceb4bc6"/>
 </x:worksheet>
 </file>
 
@@ -7248,11 +7254,11 @@
         <x:v>Research cutoff</x:v>
       </x:c>
       <x:c r="D8" s="17" t="d">
-        <x:v>2026-10-16T00:00:00.000Z</x:v>
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="26" t="str">
-        <x:v>Reviewed through 16 Oct 2026 Beijing time; latest observations in S18/S19.</x:v>
+        <x:v>Reviewed through 23 Oct 2026 Beijing time; S18/S19 and S20-S24.</x:v>
       </x:c>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
@@ -7408,7 +7414,7 @@
       </x:c>
       <x:c r="E15" s="4"/>
       <x:c r="F15" s="26" t="str">
-        <x:v>Investor discussion reported 16 Oct Beijing time [S18]; not a priced offer.</x:v>
+        <x:v>USD1.5tn discussion reaffirmed 22 Oct [S20]; offering not priced.</x:v>
       </x:c>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="4"/>
@@ -8192,13 +8198,13 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="E45" s="45" t="str">
-        <x:v>16-Oct-26 BJT</x:v>
+        <x:v>22-Oct-26 BJT</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
         <x:v>Media-reported</x:v>
       </x:c>
       <x:c r="G45" s="4" t="str">
-        <x:v>S18</x:v>
+        <x:v>S20</x:v>
       </x:c>
       <x:c r="H45" s="5"/>
       <x:c r="I45" s="5"/>
@@ -9841,6 +9847,56 @@
       <x:c r="L130" s="5"/>
       <x:c r="M130" s="5"/>
       <x:c r="N130" s="5"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="C131" t="str">
+        <x:v>S20. Reuters, 22 Oct 22:51 Beijing; November IPO timetable is provisional.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="C132" t="str">
+        <x:v>https://uk.marketscreener.com/news/anthropic-ipo-stands-alone-as-ai-market-jitters-sideline-others-ce785cdeda8cf026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="C134" t="str">
+        <x:v>S21. Anthropic, 18 Oct: 5% public-benefit share commitment, subject to shareholder approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="C135" t="str">
+        <x:v>https://www.anthropic.com/news/public-benefit-fund</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="C137" t="str">
+        <x:v>S22. Claude Duet, 21 Oct: US Pro/Max research preview, with shared plan limits.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="C138" t="str">
+        <x:v>https://claude.com/resources/articles/claude-duet</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="C140" t="str">
+        <x:v>S23. Claude Platform on Google Cloud, 22 Oct: Anthropic managed service generally available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="C141" t="str">
+        <x:v>https://claude.com/resources/articles/claude-models-on-google-cloud-anthropic-managed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="C143" t="str">
+        <x:v>S24. Agent Skills donated to AAIF, 22 Oct; no quantified revenue or cash-flow uplift.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="C144" t="str">
+        <x:v>https://www.anthropic.com/news/donating-agent-skills-to-the-agentic-ai-foundation</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">

--- a/anthropic/2026-10-11/Anthropic_IPO_Basic_Valuation.xlsx
+++ b/anthropic/2026-10-11/Anthropic_IPO_Basic_Valuation.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="1" r:id="R156dd3a3bc414374"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="2" r:id="Rab9a618d17d145b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" r:id="R9c8d8dfec6494bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="1" r:id="Rb1c8cbca6e464b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="2" r:id="Ra6e1ac5902c34657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" r:id="Rf332ddc1be3f42f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="13">
+  <x:numFmts count="15">
     <x:numFmt numFmtId="200" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <x:numFmt numFmtId="201" formatCode="dd-mmm-yyyy"/>
     <x:numFmt numFmtId="202" formatCode="$#,##0.0;($#,##0.0);&quot;-&quot;"/>
@@ -29,8 +29,10 @@
     <x:numFmt numFmtId="210" formatCode="0.0"/>
     <x:numFmt numFmtId="211" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="212" formatCode="0.0%"/>
+    <x:numFmt numFmtId="213" formatCode="#,##0.000;(#,##0.000);&quot;-&quot;"/>
+    <x:numFmt numFmtId="214" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="20">
+  <x:fonts count="21">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -143,8 +145,12 @@
       <x:color rgb="FF008000"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -169,6 +175,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8EDF2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF31465A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF31465A"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -202,7 +218,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="127">
+  <x:cellXfs count="147">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -578,6 +594,52 @@
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="212" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="214" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -935,7 +997,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc46b2f0bb52f41e5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5e34ead76c654ded"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -965,7 +1027,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R03cba60d29ad459d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R39b5a0c876844dbe"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1226,7 +1288,7 @@
       <x:c r="A3" s="3"/>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="9" t="str">
-        <x:v>USD billions. Research: 11 Oct 2026. Valuation date: assumed 31 Dec 2026.</x:v>
+        <x:v>USD billions. S-1 review: 26 Oct 2026. Valuation date remains assumed 31 Dec 2026.</x:v>
       </x:c>
       <x:c r="D3" s="5"/>
       <x:c r="E3" s="5"/>
@@ -1849,7 +1911,7 @@
       </x:c>
       <x:c r="D31" s="91" t="n">
         <x:f>D30/'Inputs'!D37-1</x:f>
-        <x:v>12.913043478260871</x:v>
+        <x:v>12.95856052344602</x:v>
       </x:c>
       <x:c r="E31" s="91" t="n">
         <x:f>'Inputs'!E23</x:f>
@@ -3315,7 +3377,7 @@
       </x:c>
       <x:c r="E81" s="4"/>
       <x:c r="F81" s="26" t="str">
-        <x:v>Actual share count is unavailable. Enter fully converted pre-offer shares.</x:v>
+        <x:v>Final IPO share count remains blank; historical shares cannot determine an offer price.</x:v>
       </x:c>
       <x:c r="G81" s="4"/>
       <x:c r="H81" s="4"/>
@@ -3737,7 +3799,7 @@
       <x:c r="A101" s="3"/>
       <x:c r="B101" s="3"/>
       <x:c r="C101" s="9" t="str">
-        <x:v>Net cash is assumed zero, so enterprise value equals equity value throughout.</x:v>
+        <x:v>Active December net-cash assumption remains zero; separate June snapshot sensitivities are shown below.</x:v>
       </x:c>
       <x:c r="D101" s="5"/>
       <x:c r="E101" s="5"/>
@@ -3877,9 +3939,9 @@
       <x:c r="C109" s="3" t="str">
         <x:v>Reported Q1-Q3 revenue (USD bn)</x:v>
       </x:c>
-      <x:c r="D109" s="125" t="n">
+      <x:c r="D109" s="128" t="n">
         <x:f>SUM('Inputs'!J37:J39)</x:f>
-        <x:v>33.1</x:v>
+        <x:v>33.086</x:v>
       </x:c>
       <x:c r="E109" s="5"/>
       <x:c r="F109" s="5"/>
@@ -3898,7 +3960,7 @@
       <x:c r="C110" s="3" t="str">
         <x:v>FY2026 revenue assumption (USD bn)</x:v>
       </x:c>
-      <x:c r="D110" s="125" t="n">
+      <x:c r="D110" s="128" t="n">
         <x:f>'Inputs'!D22</x:f>
         <x:v>64</x:v>
       </x:c>
@@ -3919,9 +3981,9 @@
       <x:c r="C111" s="3" t="str">
         <x:v>Q4 revenue needed (USD bn)</x:v>
       </x:c>
-      <x:c r="D111" s="125" t="n">
+      <x:c r="D111" s="128" t="n">
         <x:f>D110-D109</x:f>
-        <x:v>30.9</x:v>
+        <x:v>30.914</x:v>
       </x:c>
       <x:c r="E111" s="5"/>
       <x:c r="F111" s="5"/>
@@ -3942,7 +4004,7 @@
       </x:c>
       <x:c r="D112" s="126" t="n">
         <x:f>D111/'Inputs'!J39-1</x:f>
-        <x:v>0.8392857142857142</x:v>
+        <x:v>0.8401190476190477</x:v>
       </x:c>
       <x:c r="E112" s="5"/>
       <x:c r="F112" s="5"/>
@@ -3975,7 +4037,7 @@
       <x:c r="A114" s="3"/>
       <x:c r="B114" s="3"/>
       <x:c r="C114" s="3" t="str">
-        <x:v>23 Oct review: USD1.5tn discussion retained; new product/governance news does not change cash-flow inputs.</x:v>
+        <x:v>26 Oct S-1 included: Q1/Q2 are exact filing values; Q3 remains Reuters-reported.</x:v>
       </x:c>
       <x:c r="D114" s="5"/>
       <x:c r="E114" s="5"/>
@@ -3993,7 +4055,7 @@
       <x:c r="A115" s="3"/>
       <x:c r="B115" s="3"/>
       <x:c r="C115" s="3" t="str">
-        <x:v>Public-benefit share commitment is conditional; no mechanical 5% EV haircut or assumed dilution.</x:v>
+        <x:v>S-1 annuals are audited; interim statements are unaudited. Forecasts remain assumptions.</x:v>
       </x:c>
       <x:c r="D115" s="5"/>
       <x:c r="E115" s="5"/>
@@ -4011,7 +4073,7 @@
       <x:c r="A116" s="3"/>
       <x:c r="B116" s="3"/>
       <x:c r="C116" s="3" t="str">
-        <x:v>The 26 Oct public S-1 is a subsequent event, excluded from the 23 Oct valuation information set.</x:v>
+        <x:v>June liquidity is not December net cash. Amazon conversion is subject to an ownership cap.</x:v>
       </x:c>
       <x:c r="D116" s="5"/>
       <x:c r="E116" s="5"/>
@@ -4041,29 +4103,38 @@
       <x:c r="M117" s="5"/>
       <x:c r="N117" s="5"/>
     </x:row>
-    <x:row r="118" ht="21" customHeight="1">
+    <x:row r="118" ht="25" customHeight="1">
       <x:c r="A118" s="3"/>
       <x:c r="B118" s="3"/>
-      <x:c r="C118" s="3"/>
-      <x:c r="D118" s="5"/>
-      <x:c r="E118" s="5"/>
-      <x:c r="F118" s="5"/>
-      <x:c r="G118" s="5"/>
-      <x:c r="H118" s="5"/>
-      <x:c r="I118" s="5"/>
-      <x:c r="J118" s="5"/>
-      <x:c r="K118" s="5"/>
-      <x:c r="L118" s="5"/>
-      <x:c r="M118" s="5"/>
-      <x:c r="N118" s="5"/>
-    </x:row>
-    <x:row r="119" ht="21" customHeight="1">
+      <x:c r="C118" s="144" t="str">
+        <x:v>S1 operating observations (USD bn)</x:v>
+      </x:c>
+      <x:c r="D118" s="145"/>
+      <x:c r="E118" s="145"/>
+      <x:c r="F118" s="145"/>
+      <x:c r="G118" s="145"/>
+      <x:c r="H118" s="145"/>
+      <x:c r="I118" s="145"/>
+      <x:c r="J118" s="145"/>
+      <x:c r="K118" s="145"/>
+      <x:c r="L118" s="145"/>
+      <x:c r="M118" s="145"/>
+      <x:c r="N118" s="145"/>
+    </x:row>
+    <x:row r="119" ht="23" customHeight="1">
       <x:c r="A119" s="3"/>
       <x:c r="B119" s="3"/>
-      <x:c r="C119" s="3"/>
-      <x:c r="D119" s="5"/>
+      <x:c r="C119" s="3" t="str">
+        <x:v>H1 2026 revenue</x:v>
+      </x:c>
+      <x:c r="D119" s="132" t="n">
+        <x:f>'Inputs'!F149</x:f>
+        <x:v>16.286</x:v>
+      </x:c>
       <x:c r="E119" s="5"/>
-      <x:c r="F119" s="5"/>
+      <x:c r="F119" s="5" t="str">
+        <x:v>H1 interim statements are unaudited; Q3 revenue remains a separate media observation.</x:v>
+      </x:c>
       <x:c r="G119" s="5"/>
       <x:c r="H119" s="5"/>
       <x:c r="I119" s="5"/>
@@ -4073,11 +4144,16 @@
       <x:c r="M119" s="5"/>
       <x:c r="N119" s="5"/>
     </x:row>
-    <x:row r="120" ht="21" customHeight="1">
+    <x:row r="120" ht="23" customHeight="1">
       <x:c r="A120" s="3"/>
       <x:c r="B120" s="3"/>
-      <x:c r="C120" s="3"/>
-      <x:c r="D120" s="5"/>
+      <x:c r="C120" s="3" t="str">
+        <x:v>H1 operating income (loss)</x:v>
+      </x:c>
+      <x:c r="D120" s="132" t="n">
+        <x:f>'Inputs'!F150</x:f>
+        <x:v>-0.693</x:v>
+      </x:c>
       <x:c r="E120" s="5"/>
       <x:c r="F120" s="5"/>
       <x:c r="G120" s="5"/>
@@ -4089,11 +4165,16 @@
       <x:c r="M120" s="5"/>
       <x:c r="N120" s="5"/>
     </x:row>
-    <x:row r="121" ht="21" customHeight="1">
+    <x:row r="121" ht="23" customHeight="1">
       <x:c r="A121" s="3"/>
       <x:c r="B121" s="3"/>
-      <x:c r="C121" s="3"/>
-      <x:c r="D121" s="5"/>
+      <x:c r="C121" s="3" t="str">
+        <x:v>H1 net income (loss)</x:v>
+      </x:c>
+      <x:c r="D121" s="132" t="n">
+        <x:f>'Inputs'!F151</x:f>
+        <x:v>-80.748</x:v>
+      </x:c>
       <x:c r="E121" s="5"/>
       <x:c r="F121" s="5"/>
       <x:c r="G121" s="5"/>
@@ -4105,11 +4186,16 @@
       <x:c r="M121" s="5"/>
       <x:c r="N121" s="5"/>
     </x:row>
-    <x:row r="122" ht="21" customHeight="1">
+    <x:row r="122" ht="23" customHeight="1">
       <x:c r="A122" s="3"/>
       <x:c r="B122" s="3"/>
-      <x:c r="C122" s="3"/>
-      <x:c r="D122" s="5"/>
+      <x:c r="C122" s="3" t="str">
+        <x:v>H1 operating cash flow</x:v>
+      </x:c>
+      <x:c r="D122" s="132" t="n">
+        <x:f>'Inputs'!F153</x:f>
+        <x:v>3.929</x:v>
+      </x:c>
       <x:c r="E122" s="5"/>
       <x:c r="F122" s="5"/>
       <x:c r="G122" s="5"/>
@@ -4121,13 +4207,20 @@
       <x:c r="M122" s="5"/>
       <x:c r="N122" s="5"/>
     </x:row>
-    <x:row r="123" ht="21" customHeight="1">
+    <x:row r="123" ht="23" customHeight="1">
       <x:c r="A123" s="3"/>
       <x:c r="B123" s="3"/>
-      <x:c r="C123" s="3"/>
-      <x:c r="D123" s="5"/>
+      <x:c r="C123" s="3" t="str">
+        <x:v>H1 cash flow less cash capex</x:v>
+      </x:c>
+      <x:c r="D123" s="132" t="n">
+        <x:f>D122-'Inputs'!F154</x:f>
+        <x:v>3.447</x:v>
+      </x:c>
       <x:c r="E123" s="5"/>
-      <x:c r="F123" s="5"/>
+      <x:c r="F123" s="5" t="str">
+        <x:v>Cash-flow less cash capex is not unlevered FCF; vendor-payment timing affects operating cash flow.</x:v>
+      </x:c>
       <x:c r="G123" s="5"/>
       <x:c r="H123" s="5"/>
       <x:c r="I123" s="5"/>
@@ -4137,11 +4230,16 @@
       <x:c r="M123" s="5"/>
       <x:c r="N123" s="5"/>
     </x:row>
-    <x:row r="124" ht="21" customHeight="1">
+    <x:row r="124" ht="23" customHeight="1">
       <x:c r="A124" s="3"/>
       <x:c r="B124" s="3"/>
-      <x:c r="C124" s="3"/>
-      <x:c r="D124" s="5"/>
+      <x:c r="C124" s="3" t="str">
+        <x:v>H1 financing fair-value loss</x:v>
+      </x:c>
+      <x:c r="D124" s="132" t="n">
+        <x:f>'Inputs'!F152</x:f>
+        <x:v>72.388</x:v>
+      </x:c>
       <x:c r="E124" s="5"/>
       <x:c r="F124" s="5"/>
       <x:c r="G124" s="5"/>
@@ -4153,11 +4251,11 @@
       <x:c r="M124" s="5"/>
       <x:c r="N124" s="5"/>
     </x:row>
-    <x:row r="125" ht="21" customHeight="1">
+    <x:row r="125" ht="23" customHeight="1">
       <x:c r="A125" s="3"/>
       <x:c r="B125" s="3"/>
       <x:c r="C125" s="3"/>
-      <x:c r="D125" s="5"/>
+      <x:c r="D125" s="132"/>
       <x:c r="E125" s="5"/>
       <x:c r="F125" s="5"/>
       <x:c r="G125" s="5"/>
@@ -4169,27 +4267,34 @@
       <x:c r="M125" s="5"/>
       <x:c r="N125" s="5"/>
     </x:row>
-    <x:row r="126" ht="21" customHeight="1">
+    <x:row r="126" ht="25" customHeight="1">
       <x:c r="A126" s="3"/>
       <x:c r="B126" s="3"/>
-      <x:c r="C126" s="3"/>
-      <x:c r="D126" s="5"/>
-      <x:c r="E126" s="5"/>
-      <x:c r="F126" s="5"/>
-      <x:c r="G126" s="5"/>
-      <x:c r="H126" s="5"/>
-      <x:c r="I126" s="5"/>
-      <x:c r="J126" s="5"/>
-      <x:c r="K126" s="5"/>
-      <x:c r="L126" s="5"/>
-      <x:c r="M126" s="5"/>
-      <x:c r="N126" s="5"/>
-    </x:row>
-    <x:row r="127" ht="21" customHeight="1">
+      <x:c r="C126" s="144" t="str">
+        <x:v>June cash bridge sensitivity (USD bn)</x:v>
+      </x:c>
+      <x:c r="D126" s="146"/>
+      <x:c r="E126" s="145"/>
+      <x:c r="F126" s="145"/>
+      <x:c r="G126" s="145"/>
+      <x:c r="H126" s="145"/>
+      <x:c r="I126" s="145"/>
+      <x:c r="J126" s="145"/>
+      <x:c r="K126" s="145"/>
+      <x:c r="L126" s="145"/>
+      <x:c r="M126" s="145"/>
+      <x:c r="N126" s="145"/>
+    </x:row>
+    <x:row r="127" ht="23" customHeight="1">
       <x:c r="A127" s="3"/>
       <x:c r="B127" s="3"/>
-      <x:c r="C127" s="3"/>
-      <x:c r="D127" s="5"/>
+      <x:c r="C127" s="3" t="str">
+        <x:v>Cash plus short-term investments</x:v>
+      </x:c>
+      <x:c r="D127" s="132" t="n">
+        <x:f>SUM('Inputs'!D161:D162)</x:f>
+        <x:v>131.651</x:v>
+      </x:c>
       <x:c r="E127" s="5"/>
       <x:c r="F127" s="5"/>
       <x:c r="G127" s="5"/>
@@ -4201,11 +4306,16 @@
       <x:c r="M127" s="5"/>
       <x:c r="N127" s="5"/>
     </x:row>
-    <x:row r="128" ht="21" customHeight="1">
+    <x:row r="128" ht="23" customHeight="1">
       <x:c r="A128" s="3"/>
       <x:c r="B128" s="3"/>
-      <x:c r="C128" s="3"/>
-      <x:c r="D128" s="5"/>
+      <x:c r="C128" s="3" t="str">
+        <x:v>Less: finance lease liabilities</x:v>
+      </x:c>
+      <x:c r="D128" s="132" t="n">
+        <x:f>'Inputs'!D167</x:f>
+        <x:v>0.443</x:v>
+      </x:c>
       <x:c r="E128" s="5"/>
       <x:c r="F128" s="5"/>
       <x:c r="G128" s="5"/>
@@ -4217,11 +4327,16 @@
       <x:c r="M128" s="5"/>
       <x:c r="N128" s="5"/>
     </x:row>
-    <x:row r="129" ht="21" customHeight="1">
+    <x:row r="129" ht="23" customHeight="1">
       <x:c r="A129" s="3"/>
       <x:c r="B129" s="3"/>
-      <x:c r="C129" s="3"/>
-      <x:c r="D129" s="5"/>
+      <x:c r="C129" s="3" t="str">
+        <x:v>Amazon note principal</x:v>
+      </x:c>
+      <x:c r="D129" s="132" t="n">
+        <x:f>SUM('Inputs'!D165:D166)</x:f>
+        <x:v>6.203</x:v>
+      </x:c>
       <x:c r="E129" s="5"/>
       <x:c r="F129" s="5"/>
       <x:c r="G129" s="5"/>
@@ -4233,11 +4348,16 @@
       <x:c r="M129" s="5"/>
       <x:c r="N129" s="5"/>
     </x:row>
-    <x:row r="130" ht="21" customHeight="1">
+    <x:row r="130" ht="23" customHeight="1">
       <x:c r="A130" s="3"/>
       <x:c r="B130" s="3"/>
-      <x:c r="C130" s="3"/>
-      <x:c r="D130" s="5"/>
+      <x:c r="C130" s="3" t="str">
+        <x:v>Cash proxy: notes retained</x:v>
+      </x:c>
+      <x:c r="D130" s="132" t="n">
+        <x:f>D127-SUM(D128:D129)</x:f>
+        <x:v>125.00500000000001</x:v>
+      </x:c>
       <x:c r="E130" s="5"/>
       <x:c r="F130" s="5"/>
       <x:c r="G130" s="5"/>
@@ -4248,6 +4368,193 @@
       <x:c r="L130" s="5"/>
       <x:c r="M130" s="5"/>
       <x:c r="N130" s="5"/>
+    </x:row>
+    <x:row r="131" ht="23" customHeight="1">
+      <x:c r="C131" s="129" t="str">
+        <x:v>Cash proxy: full conversion</x:v>
+      </x:c>
+      <x:c r="D131" s="130" t="n">
+        <x:f>D127-D128</x:f>
+        <x:v>131.208</x:v>
+      </x:c>
+      <x:c r="E131" s="129"/>
+      <x:c r="F131" s="129"/>
+      <x:c r="G131" s="129"/>
+      <x:c r="H131" s="129"/>
+      <x:c r="I131" s="129"/>
+      <x:c r="J131" s="129"/>
+      <x:c r="K131" s="129"/>
+      <x:c r="L131" s="129"/>
+      <x:c r="M131" s="129"/>
+      <x:c r="N131" s="129"/>
+    </x:row>
+    <x:row r="132" ht="23" customHeight="1">
+      <x:c r="C132" s="129" t="str">
+        <x:v>DCF equity: notes retained</x:v>
+      </x:c>
+      <x:c r="D132" s="130" t="n">
+        <x:f>$D$8+D130</x:f>
+        <x:v>913.5444443995485</x:v>
+      </x:c>
+      <x:c r="E132" s="129"/>
+      <x:c r="F132" s="129"/>
+      <x:c r="G132" s="129"/>
+      <x:c r="H132" s="129"/>
+      <x:c r="I132" s="129"/>
+      <x:c r="J132" s="129"/>
+      <x:c r="K132" s="129"/>
+      <x:c r="L132" s="129"/>
+      <x:c r="M132" s="129"/>
+      <x:c r="N132" s="129"/>
+    </x:row>
+    <x:row r="133" ht="23" customHeight="1">
+      <x:c r="C133" s="129" t="str">
+        <x:v>DCF equity: full conversion</x:v>
+      </x:c>
+      <x:c r="D133" s="130" t="n">
+        <x:f>$D$8+D131</x:f>
+        <x:v>919.7474443995485</x:v>
+      </x:c>
+      <x:c r="E133" s="129"/>
+      <x:c r="F133" s="129"/>
+      <x:c r="G133" s="129"/>
+      <x:c r="H133" s="129"/>
+      <x:c r="I133" s="129"/>
+      <x:c r="J133" s="129"/>
+      <x:c r="K133" s="129"/>
+      <x:c r="L133" s="129"/>
+      <x:c r="M133" s="129"/>
+      <x:c r="N133" s="129"/>
+    </x:row>
+    <x:row r="134" ht="23" customHeight="1">
+      <x:c r="C134" s="129" t="str">
+        <x:v>Terminal margin: notes retained</x:v>
+      </x:c>
+      <x:c r="D134" s="133" t="n">
+        <x:f>((D10-D130-D56)/N42*('Inputs'!D11-'Inputs'!D13)-SUM(D50:D52))/D46/(1-'Inputs'!D14)</x:f>
+        <x:v>0.7171122588175671</x:v>
+      </x:c>
+      <x:c r="E134" s="129"/>
+      <x:c r="F134" s="129"/>
+      <x:c r="G134" s="129"/>
+      <x:c r="H134" s="129"/>
+      <x:c r="I134" s="129"/>
+      <x:c r="J134" s="129"/>
+      <x:c r="K134" s="129"/>
+      <x:c r="L134" s="129"/>
+      <x:c r="M134" s="129"/>
+      <x:c r="N134" s="129"/>
+    </x:row>
+    <x:row r="135" ht="23" customHeight="1">
+      <x:c r="C135" s="129" t="str">
+        <x:v>Terminal margin: full conversion</x:v>
+      </x:c>
+      <x:c r="D135" s="133" t="n">
+        <x:f>((D10-D131-D56)/N42*('Inputs'!D11-'Inputs'!D13)-SUM(D50:D52))/D46/(1-'Inputs'!D14)</x:f>
+        <x:v>0.7132292751546129</x:v>
+      </x:c>
+      <x:c r="E135" s="129"/>
+      <x:c r="F135" s="129"/>
+      <x:c r="G135" s="129"/>
+      <x:c r="H135" s="129"/>
+      <x:c r="I135" s="129"/>
+      <x:c r="J135" s="129"/>
+      <x:c r="K135" s="129"/>
+      <x:c r="L135" s="129"/>
+      <x:c r="M135" s="129"/>
+      <x:c r="N135" s="129"/>
+    </x:row>
+    <x:row r="136" ht="23" customHeight="1">
+      <x:c r="C136" s="129"/>
+      <x:c r="D136" s="129"/>
+      <x:c r="E136" s="129"/>
+      <x:c r="F136" s="129"/>
+      <x:c r="G136" s="129"/>
+      <x:c r="H136" s="129"/>
+      <x:c r="I136" s="129"/>
+      <x:c r="J136" s="129"/>
+      <x:c r="K136" s="129"/>
+      <x:c r="L136" s="129"/>
+      <x:c r="M136" s="129"/>
+      <x:c r="N136" s="129"/>
+    </x:row>
+    <x:row r="137" ht="23" customHeight="1">
+      <x:c r="C137" s="129" t="str">
+        <x:v>June snapshot only: no H2 cash roll-forward, new funding or IPO proceeds; not an existing-common equity allocation.</x:v>
+      </x:c>
+      <x:c r="D137" s="129"/>
+      <x:c r="E137" s="129"/>
+      <x:c r="F137" s="129"/>
+      <x:c r="G137" s="129"/>
+      <x:c r="H137" s="129"/>
+      <x:c r="I137" s="129"/>
+      <x:c r="J137" s="129"/>
+      <x:c r="K137" s="129"/>
+      <x:c r="L137" s="129"/>
+      <x:c r="M137" s="129"/>
+      <x:c r="N137" s="129"/>
+    </x:row>
+    <x:row r="138" ht="23" customHeight="1">
+      <x:c r="C138" s="129" t="str">
+        <x:v>Full conversion is illustrative, subject to Amazon 12% ownership cap; residual notes may remain outstanding.</x:v>
+      </x:c>
+      <x:c r="D138" s="129"/>
+      <x:c r="E138" s="129"/>
+      <x:c r="F138" s="129"/>
+      <x:c r="G138" s="129"/>
+      <x:c r="H138" s="129"/>
+      <x:c r="I138" s="129"/>
+      <x:c r="J138" s="129"/>
+      <x:c r="K138" s="129"/>
+      <x:c r="L138" s="129"/>
+      <x:c r="M138" s="129"/>
+      <x:c r="N138" s="129"/>
+    </x:row>
+    <x:row r="139" ht="23" customHeight="1">
+      <x:c r="C139" s="129" t="str">
+        <x:v>Restricted cash is excluded. Operating rent remains in forecast margins and is not deducted a second time.</x:v>
+      </x:c>
+      <x:c r="D139" s="129"/>
+      <x:c r="E139" s="129"/>
+      <x:c r="F139" s="129"/>
+      <x:c r="G139" s="129"/>
+      <x:c r="H139" s="129"/>
+      <x:c r="I139" s="129"/>
+      <x:c r="J139" s="129"/>
+      <x:c r="K139" s="129"/>
+      <x:c r="L139" s="129"/>
+      <x:c r="M139" s="129"/>
+      <x:c r="N139" s="129"/>
+    </x:row>
+    <x:row r="140" ht="23" customHeight="1">
+      <x:c r="C140" s="129" t="str">
+        <x:v>The USD108.566bn note carrying value is not the USD6.203bn cash principal.</x:v>
+      </x:c>
+      <x:c r="D140" s="129"/>
+      <x:c r="E140" s="129"/>
+      <x:c r="F140" s="129"/>
+      <x:c r="G140" s="129"/>
+      <x:c r="H140" s="129"/>
+      <x:c r="I140" s="129"/>
+      <x:c r="J140" s="129"/>
+      <x:c r="K140" s="129"/>
+      <x:c r="L140" s="129"/>
+      <x:c r="M140" s="129"/>
+      <x:c r="N140" s="129"/>
+    </x:row>
+    <x:row r="141" ht="23" customHeight="1">
+      <x:c r="C141" s="129"/>
+      <x:c r="D141" s="129"/>
+      <x:c r="E141" s="129"/>
+      <x:c r="F141" s="129"/>
+      <x:c r="G141" s="129"/>
+      <x:c r="H141" s="129"/>
+      <x:c r="I141" s="129"/>
+      <x:c r="J141" s="129"/>
+      <x:c r="K141" s="129"/>
+      <x:c r="L141" s="129"/>
+      <x:c r="M141" s="129"/>
+      <x:c r="N141" s="129"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D67:I71">
@@ -4263,7 +4570,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R499c812c8ceb4bc6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500a6ec34ab449ec"/>
 </x:worksheet>
 </file>
 
@@ -7161,7 +7468,7 @@
       <x:c r="A3" s="3"/>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="9" t="str">
-        <x:v>Blue cells are editable assumptions. Green cells link to published inputs. Update cutoff: 11 Oct 2026.</x:v>
+        <x:v>USD billions. S-1 review: 26 Oct 2026. Annuals audited; interim statements unaudited.</x:v>
       </x:c>
       <x:c r="D3" s="5"/>
       <x:c r="E3" s="5"/>
@@ -7254,11 +7561,11 @@
         <x:v>Research cutoff</x:v>
       </x:c>
       <x:c r="D8" s="17" t="d">
-        <x:v>2026-10-23T00:00:00.000Z</x:v>
+        <x:v>2026-10-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="26" t="str">
-        <x:v>Reviewed through 23 Oct 2026 Beijing time; S18/S19 and S20-S24.</x:v>
+        <x:v>Public S-1 included [S25]; filing PDF conversion used; EDGAR HTML retrieval blocked.</x:v>
       </x:c>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
@@ -7347,7 +7654,7 @@
       </x:c>
       <x:c r="E12" s="4"/>
       <x:c r="F12" s="26" t="str">
-        <x:v>Assumed zero. Current cash, debt and conversion adjustments are unavailable.</x:v>
+        <x:v>Zero remains a Dec-2026 assumption. June liquidity and debt sensitivities appear below.</x:v>
       </x:c>
       <x:c r="G12" s="4"/>
       <x:c r="H12" s="4"/>
@@ -7434,7 +7741,7 @@
       <x:c r="D16" s="15"/>
       <x:c r="E16" s="4"/>
       <x:c r="F16" s="26" t="str">
-        <x:v>Reported at up to $100bn by the WSJ [S12]. Exclude secondary sales.</x:v>
+        <x:v>Public S-1 leaves offering size blank. Proceeds remain an unfilled input.</x:v>
       </x:c>
       <x:c r="G16" s="4"/>
       <x:c r="H16" s="4"/>
@@ -7476,7 +7783,7 @@
       <x:c r="D18" s="24"/>
       <x:c r="E18" s="4"/>
       <x:c r="F18" s="26" t="str">
-        <x:v>Enter shares after all pre-IPO conversions. Actual count is unavailable.</x:v>
+        <x:v>Final post-conversion diluted offering share count remains blank in the S-1.</x:v>
       </x:c>
       <x:c r="G18" s="4"/>
       <x:c r="H18" s="4"/>
@@ -7954,35 +8261,36 @@
       <x:c r="A37" s="3"/>
       <x:c r="B37" s="3"/>
       <x:c r="C37" s="3" t="str">
-        <x:v>Revenue, approximately</x:v>
-      </x:c>
-      <x:c r="D37" s="44" t="n">
-        <x:v>4.6</x:v>
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="D37" s="142" t="n">
+        <x:f>D149</x:f>
+        <x:v>4.585</x:v>
       </x:c>
       <x:c r="E37" s="45" t="str">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F37" s="4" t="str">
-        <x:v>Media-reported</x:v>
+        <x:v>S-1 audited</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>S3</x:v>
+        <x:v>S25</x:v>
       </x:c>
       <x:c r="H37" s="5"/>
       <x:c r="I37" s="3" t="str">
         <x:v>2026Q1</x:v>
       </x:c>
-      <x:c r="J37" s="123" t="n">
-        <x:v>4.7</x:v>
+      <x:c r="J37" s="127" t="n">
+        <x:v>4.731</x:v>
       </x:c>
       <x:c r="K37" s="124" t="d">
-        <x:v>2026-10-15T00:00:00.000Z</x:v>
+        <x:v>2026-10-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
-        <x:v>Media-reported</x:v>
+        <x:v>S-1 unaudited</x:v>
       </x:c>
       <x:c r="M37" s="4" t="str">
-        <x:v>S19</x:v>
+        <x:v>S25</x:v>
       </x:c>
       <x:c r="N37" s="5"/>
     </x:row>
@@ -7990,35 +8298,36 @@
       <x:c r="A38" s="3"/>
       <x:c r="B38" s="3"/>
       <x:c r="C38" s="3" t="str">
-        <x:v>Operating loss, more than</x:v>
-      </x:c>
-      <x:c r="D38" s="44" t="n">
-        <x:v>-8</x:v>
+        <x:v>Operating income (loss)</x:v>
+      </x:c>
+      <x:c r="D38" s="142" t="n">
+        <x:f>D150</x:f>
+        <x:v>-8.06</x:v>
       </x:c>
       <x:c r="E38" s="45" t="str">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>Media-reported</x:v>
+        <x:v>S-1 audited</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
-        <x:v>S3</x:v>
+        <x:v>S25</x:v>
       </x:c>
       <x:c r="H38" s="5"/>
       <x:c r="I38" s="3" t="str">
         <x:v>2026Q2</x:v>
       </x:c>
-      <x:c r="J38" s="123" t="n">
-        <x:v>11.6</x:v>
+      <x:c r="J38" s="127" t="n">
+        <x:v>11.555</x:v>
       </x:c>
       <x:c r="K38" s="124" t="d">
-        <x:v>2026-10-15T00:00:00.000Z</x:v>
+        <x:v>2026-10-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="L38" s="4" t="str">
-        <x:v>Media-reported</x:v>
+        <x:v>S-1 unaudited</x:v>
       </x:c>
       <x:c r="M38" s="4" t="str">
-        <x:v>S19</x:v>
+        <x:v>S25</x:v>
       </x:c>
       <x:c r="N38" s="5"/>
     </x:row>
@@ -8044,14 +8353,14 @@
       <x:c r="I39" s="3" t="str">
         <x:v>2026Q3</x:v>
       </x:c>
-      <x:c r="J39" s="123" t="n">
+      <x:c r="J39" s="127" t="n">
         <x:v>16.8</x:v>
       </x:c>
       <x:c r="K39" s="124" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="L39" s="4" t="str">
-        <x:v>Media-reported</x:v>
+        <x:v>Reuters; not S-1</x:v>
       </x:c>
       <x:c r="M39" s="4" t="str">
         <x:v>S19</x:v>
@@ -8218,16 +8527,16 @@
       <x:c r="A46" s="3"/>
       <x:c r="B46" s="3"/>
       <x:c r="C46" s="3" t="str">
-        <x:v>Long-term compute commitments, at least</x:v>
+        <x:v>Prior Reuters compute observation</x:v>
       </x:c>
       <x:c r="D46" s="44" t="n">
         <x:v>518</x:v>
       </x:c>
       <x:c r="E46" s="45" t="str">
-        <x:v>Oct-26</x:v>
+        <x:v>15-Oct-26</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
-        <x:v>Media-reported</x:v>
+        <x:v>Historical report</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
         <x:v>S19</x:v>
@@ -9896,6 +10205,448 @@
     <x:row r="144">
       <x:c r="C144" t="str">
         <x:v>https://www.anthropic.com/news/donating-agent-skills-to-the-agentic-ai-foundation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="C146" t="str">
+        <x:v>S1 actuals in USD bn: FY2025 audited; H1 periods and quarterly MD&amp;A unaudited.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="25" customHeight="1">
+      <x:c r="C148" s="143" t="str">
+        <x:v>S1 actuals</x:v>
+      </x:c>
+      <x:c r="D148" s="143" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="E148" s="143" t="str">
+        <x:v>H1 2025</x:v>
+      </x:c>
+      <x:c r="F148" s="143" t="str">
+        <x:v>H1 2026</x:v>
+      </x:c>
+      <x:c r="G148" s="143" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="H148" s="143" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="23" customHeight="1">
+      <x:c r="C149" s="129" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="D149" s="130" t="n">
+        <x:v>4.585</x:v>
+      </x:c>
+      <x:c r="E149" s="130" t="n">
+        <x:v>1.163</x:v>
+      </x:c>
+      <x:c r="F149" s="130" t="n">
+        <x:v>16.286</x:v>
+      </x:c>
+      <x:c r="G149" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="H149" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="23" customHeight="1">
+      <x:c r="C150" s="129" t="str">
+        <x:v>Operating income (loss)</x:v>
+      </x:c>
+      <x:c r="D150" s="130" t="n">
+        <x:v>-8.06</x:v>
+      </x:c>
+      <x:c r="E150" s="130" t="n">
+        <x:v>-2.135</x:v>
+      </x:c>
+      <x:c r="F150" s="130" t="n">
+        <x:v>-0.693</x:v>
+      </x:c>
+      <x:c r="G150" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="H150" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="23" customHeight="1">
+      <x:c r="C151" s="129" t="str">
+        <x:v>Net income (loss)</x:v>
+      </x:c>
+      <x:c r="D151" s="130" t="n">
+        <x:v>-41.965</x:v>
+      </x:c>
+      <x:c r="E151" s="130" t="n">
+        <x:v>-12.969</x:v>
+      </x:c>
+      <x:c r="F151" s="130" t="n">
+        <x:v>-80.748</x:v>
+      </x:c>
+      <x:c r="G151" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="H151" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="23" customHeight="1">
+      <x:c r="C152" s="129" t="str">
+        <x:v>Financing fair-value loss</x:v>
+      </x:c>
+      <x:c r="D152" s="130" t="n">
+        <x:v>34.308</x:v>
+      </x:c>
+      <x:c r="E152" s="130" t="n">
+        <x:v>10.942</x:v>
+      </x:c>
+      <x:c r="F152" s="130" t="n">
+        <x:v>72.388</x:v>
+      </x:c>
+      <x:c r="G152" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="H152" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="23" customHeight="1">
+      <x:c r="C153" s="129" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="D153" s="130" t="n">
+        <x:v>-2.637</x:v>
+      </x:c>
+      <x:c r="E153" s="130" t="n">
+        <x:v>-1.513</x:v>
+      </x:c>
+      <x:c r="F153" s="130" t="n">
+        <x:v>3.929</x:v>
+      </x:c>
+      <x:c r="G153" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="H153" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="23" customHeight="1">
+      <x:c r="C154" s="129" t="str">
+        <x:v>Cash capex</x:v>
+      </x:c>
+      <x:c r="D154" s="130" t="n">
+        <x:v>0.131</x:v>
+      </x:c>
+      <x:c r="E154" s="130" t="n">
+        <x:v>0.018</x:v>
+      </x:c>
+      <x:c r="F154" s="130" t="n">
+        <x:v>0.482</x:v>
+      </x:c>
+      <x:c r="G154" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="H154" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="23" customHeight="1">
+      <x:c r="C155" s="129" t="str">
+        <x:v>D&amp;A</x:v>
+      </x:c>
+      <x:c r="D155" s="130" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="E155" s="130" t="n">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="F155" s="130" t="n">
+        <x:v>0.097</x:v>
+      </x:c>
+      <x:c r="G155" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="H155" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="23" customHeight="1">
+      <x:c r="C156" s="129" t="str">
+        <x:v>Share-based compensation</x:v>
+      </x:c>
+      <x:c r="D156" s="130" t="n">
+        <x:v>1.158</x:v>
+      </x:c>
+      <x:c r="E156" s="130" t="n">
+        <x:v>0.279</x:v>
+      </x:c>
+      <x:c r="F156" s="130" t="n">
+        <x:v>2.185</x:v>
+      </x:c>
+      <x:c r="G156" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="H156" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="23" customHeight="1">
+      <x:c r="C157" s="129"/>
+      <x:c r="D157" s="129"/>
+      <x:c r="E157" s="129"/>
+      <x:c r="F157" s="129"/>
+      <x:c r="G157" s="129"/>
+      <x:c r="H157" s="129"/>
+    </x:row>
+    <x:row r="160" ht="25" customHeight="1">
+      <x:c r="C160" s="143" t="str">
+        <x:v>June 2026 balance / terms</x:v>
+      </x:c>
+      <x:c r="D160" s="143" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="E160" s="143" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="F160" s="143" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G160" s="143" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="H160" s="143"/>
+    </x:row>
+    <x:row r="161" ht="23" customHeight="1">
+      <x:c r="C161" s="129" t="str">
+        <x:v>Cash and equivalents</x:v>
+      </x:c>
+      <x:c r="D161" s="130" t="n">
+        <x:v>112.389</x:v>
+      </x:c>
+      <x:c r="E161" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F161" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G161" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H161" s="129"/>
+    </x:row>
+    <x:row r="162" ht="23" customHeight="1">
+      <x:c r="C162" s="129" t="str">
+        <x:v>Short-term investments</x:v>
+      </x:c>
+      <x:c r="D162" s="130" t="n">
+        <x:v>19.262</x:v>
+      </x:c>
+      <x:c r="E162" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F162" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G162" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H162" s="129"/>
+    </x:row>
+    <x:row r="163" ht="23" customHeight="1">
+      <x:c r="C163" s="129" t="str">
+        <x:v>Restricted cash (excluded)</x:v>
+      </x:c>
+      <x:c r="D163" s="130" t="n">
+        <x:v>2.529</x:v>
+      </x:c>
+      <x:c r="E163" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F163" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G163" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H163" s="129"/>
+    </x:row>
+    <x:row r="164" ht="23" customHeight="1">
+      <x:c r="C164" s="129" t="str">
+        <x:v>Notes at fair value</x:v>
+      </x:c>
+      <x:c r="D164" s="130" t="n">
+        <x:v>108.566</x:v>
+      </x:c>
+      <x:c r="E164" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F164" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G164" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H164" s="129"/>
+    </x:row>
+    <x:row r="165" ht="23" customHeight="1">
+      <x:c r="C165" s="129" t="str">
+        <x:v>Amazon 2023 principal</x:v>
+      </x:c>
+      <x:c r="D165" s="130" t="n">
+        <x:v>2.186</x:v>
+      </x:c>
+      <x:c r="E165" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F165" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G165" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H165" s="129"/>
+    </x:row>
+    <x:row r="166" ht="23" customHeight="1">
+      <x:c r="C166" s="129" t="str">
+        <x:v>Amazon 2024 principal</x:v>
+      </x:c>
+      <x:c r="D166" s="130" t="n">
+        <x:v>4.017</x:v>
+      </x:c>
+      <x:c r="E166" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F166" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G166" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H166" s="129"/>
+    </x:row>
+    <x:row r="167" ht="23" customHeight="1">
+      <x:c r="C167" s="129" t="str">
+        <x:v>Finance lease liabilities</x:v>
+      </x:c>
+      <x:c r="D167" s="130" t="n">
+        <x:v>0.443</x:v>
+      </x:c>
+      <x:c r="E167" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F167" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G167" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H167" s="129"/>
+    </x:row>
+    <x:row r="168" ht="23" customHeight="1">
+      <x:c r="C168" s="129" t="str">
+        <x:v>Operating lease liabilities</x:v>
+      </x:c>
+      <x:c r="D168" s="130" t="n">
+        <x:v>1.079</x:v>
+      </x:c>
+      <x:c r="E168" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F168" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G168" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H168" s="129"/>
+    </x:row>
+    <x:row r="169" ht="23" customHeight="1">
+      <x:c r="C169" s="129" t="str">
+        <x:v>Uncommenced lease obligations</x:v>
+      </x:c>
+      <x:c r="D169" s="130" t="n">
+        <x:v>321.4</x:v>
+      </x:c>
+      <x:c r="E169" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F169" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G169" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H169" s="129"/>
+    </x:row>
+    <x:row r="170" ht="23" customHeight="1">
+      <x:c r="C170" s="129" t="str">
+        <x:v>Minimum purchase commitments</x:v>
+      </x:c>
+      <x:c r="D170" s="130" t="n">
+        <x:v>265.6</x:v>
+      </x:c>
+      <x:c r="E170" s="129" t="str">
+        <x:v>USD bn</x:v>
+      </x:c>
+      <x:c r="F170" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G170" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H170" s="129"/>
+    </x:row>
+    <x:row r="171" ht="23" customHeight="1">
+      <x:c r="C171" s="129" t="str">
+        <x:v>Amazon conversion ownership cap</x:v>
+      </x:c>
+      <x:c r="D171" s="131" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="E171" s="129" t="str">
+        <x:v>fraction</x:v>
+      </x:c>
+      <x:c r="F171" s="129" t="str">
+        <x:v>S1; see notes</x:v>
+      </x:c>
+      <x:c r="G171" s="129" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="H171" s="129"/>
+    </x:row>
+    <x:row r="172" ht="23" customHeight="1">
+      <x:c r="C172" s="129"/>
+      <x:c r="D172" s="129"/>
+      <x:c r="E172" s="129"/>
+      <x:c r="F172" s="129"/>
+      <x:c r="G172" s="129"/>
+      <x:c r="H172" s="129"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="C173" t="str">
+        <x:v>Purchase commitments and uncommenced leases are separate multiyear categories, not current debt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="C175" t="str">
+        <x:v>S25. Anthropic Form S-1 filed 26 Oct 2026. MD&amp;A p160/p164; statements F-5/F-7/F-12; notes F-35/F-58.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="C176" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/2130357/000162828026067168/anthropicpbc-sx1.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="C178" t="str">
+        <x:v>Retrieval: SEC HTML blocked / reader size limit. Filing PDF conversion checked; conversion fidelity is a source limitation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="C179" t="str">
+        <x:v>https://sec2pdf.com/ANTHROPIC</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
